--- a/tests/fixtures/raw/CP02_drift.xlsx
+++ b/tests/fixtures/raw/CP02_drift.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -573,6 +573,11 @@
           <t>적용모델</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>개정일</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -621,6 +626,11 @@
         </is>
       </c>
       <c r="J4" s="4" t="n"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="6" t="n"/>
@@ -661,6 +671,11 @@
         </is>
       </c>
       <c r="J5" s="4" t="n"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="6" t="n"/>
@@ -705,6 +720,11 @@
         </is>
       </c>
       <c r="J6" s="4" t="n"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="6" t="n"/>
@@ -745,6 +765,11 @@
         </is>
       </c>
       <c r="J7" s="4" t="n"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="6" t="n"/>
@@ -789,6 +814,11 @@
         </is>
       </c>
       <c r="J8" s="4" t="n"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="6" t="n"/>
@@ -833,6 +863,11 @@
         </is>
       </c>
       <c r="J9" s="4" t="n"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="6" t="n"/>
@@ -881,6 +916,11 @@
           <t>M2</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="n"/>
@@ -925,6 +965,11 @@
         </is>
       </c>
       <c r="J11" s="4" t="n"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="n"/>
@@ -965,6 +1010,11 @@
         </is>
       </c>
       <c r="J12" s="4" t="n"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="n"/>
@@ -1005,6 +1055,11 @@
         </is>
       </c>
       <c r="J13" s="4" t="n"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="6" t="n"/>
@@ -1045,6 +1100,11 @@
         </is>
       </c>
       <c r="J14" s="4" t="n"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="n"/>
@@ -1085,6 +1145,11 @@
         </is>
       </c>
       <c r="J15" s="4" t="n"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="6" t="n"/>
@@ -1125,6 +1190,11 @@
         </is>
       </c>
       <c r="J16" s="4" t="n"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="n"/>
@@ -1169,6 +1239,11 @@
           <t>M3</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="6" t="n"/>
@@ -1213,6 +1288,11 @@
         </is>
       </c>
       <c r="J18" s="4" t="n"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="7" t="n"/>
@@ -1253,16 +1333,21 @@
         </is>
       </c>
       <c r="J19" s="4" t="n"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A4:A19"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="C11:C17"/>
+    <mergeCell ref="A2:K2"/>
     <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A2:J2"/>
     <mergeCell ref="C18:C19"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
